--- a/public/exports-from-60/29189722.xlsx
+++ b/public/exports-from-60/29189722.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -4639,7 +4639,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t xml:space="preserve">200039233</t>
+          <t xml:space="preserve">200039235</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">

--- a/public/exports-from-60/29189722.xlsx
+++ b/public/exports-from-60/29189722.xlsx
@@ -4639,7 +4639,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t xml:space="preserve">200039235</t>
+          <t xml:space="preserve">200039233</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -7489,7 +7489,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t xml:space="preserve">311428341</t>
+          <t xml:space="preserve">311428343</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">

--- a/public/exports-from-60/29189722.xlsx
+++ b/public/exports-from-60/29189722.xlsx
@@ -7489,7 +7489,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t xml:space="preserve">311428343</t>
+          <t xml:space="preserve">311428341</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
